--- a/output/yearly_surface_area_iteration_61_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_61_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497618607644</v>
+        <v>10.84497627541351</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907143269281</v>
+        <v>37.78907174398579</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.312236827679491</v>
+        <v>4.963716392671873</v>
       </c>
       <c r="C2" t="n">
-        <v>6.898741117742336</v>
+        <v>7.853981633974483</v>
       </c>
       <c r="D2" t="n">
-        <v>28.36661816650734</v>
+        <v>36.69969268015426</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.67989349515331</v>
+        <v>15.45270886484479</v>
       </c>
       <c r="C3" t="n">
-        <v>30.67470701919159</v>
+        <v>19.58095796120263</v>
       </c>
       <c r="D3" t="n">
-        <v>66.70975650357076</v>
+        <v>72.57079029792423</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.90680038802134</v>
+        <v>33.3362250454047</v>
       </c>
       <c r="C4" t="n">
-        <v>54.99456114879357</v>
+        <v>64.69422846675207</v>
       </c>
       <c r="D4" t="n">
-        <v>88.22868443295661</v>
+        <v>110.346478461933</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.68777283898307</v>
+        <v>39.66260725157115</v>
       </c>
       <c r="C5" t="n">
-        <v>120.6813365445392</v>
+        <v>113.5391219961436</v>
       </c>
       <c r="D5" t="n">
-        <v>67.91239744127311</v>
+        <v>87.35100198535997</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.03531152628644</v>
+        <v>36.79001346894498</v>
       </c>
       <c r="C6" t="n">
-        <v>154.1638419978767</v>
+        <v>123.4115769100496</v>
       </c>
       <c r="D6" t="n">
-        <v>49.3887817575443</v>
+        <v>53.53470231257858</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.23706852727577</v>
+        <v>25.09248957284423</v>
       </c>
       <c r="C7" t="n">
-        <v>130.1336034410274</v>
+        <v>112.9461463827785</v>
       </c>
       <c r="D7" t="n">
-        <v>40.18391528252619</v>
+        <v>40.96244121199391</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.10833640483241</v>
+        <v>13.18487166803466</v>
       </c>
       <c r="C8" t="n">
-        <v>83.36510630611789</v>
+        <v>78.94233289848603</v>
       </c>
       <c r="D8" t="n">
         <v>36.04977569994287</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>44.81874619427537</v>
+        <v>45.37343364717482</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
         <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.6586572839889</v>
+        <v>7.66572128392411</v>
       </c>
       <c r="C21" t="n">
-        <v>92.86121956836541</v>
+        <v>93.90508572807033</v>
       </c>
       <c r="D21" t="n">
-        <v>7.6586572839889</v>
+        <v>7.66572128392411</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.873796514508666</v>
+        <v>5.440845776935824</v>
       </c>
       <c r="C2" t="n">
-        <v>6.630723994482958</v>
+        <v>11.14578168631404</v>
       </c>
       <c r="D2" t="n">
-        <v>29.98650187851457</v>
+        <v>35.03955731227291</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.23458094805276</v>
+        <v>15.90431280879833</v>
       </c>
       <c r="C3" t="n">
-        <v>28.53940576245478</v>
+        <v>24.98057033456009</v>
       </c>
       <c r="D3" t="n">
-        <v>72.44316309637213</v>
+        <v>82.77605768356982</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.35800342134737</v>
+        <v>31.06446085777758</v>
       </c>
       <c r="C4" t="n">
-        <v>65.48551711637499</v>
+        <v>56.23254500384881</v>
       </c>
       <c r="D4" t="n">
-        <v>99.4471154493849</v>
+        <v>119.7653659364769</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.40583132141499</v>
+        <v>44.54680208019903</v>
       </c>
       <c r="C5" t="n">
-        <v>110.274810879523</v>
+        <v>116.1652971050039</v>
       </c>
       <c r="D5" t="n">
-        <v>80.82237975211868</v>
+        <v>103.0344215607028</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.75733805726436</v>
+        <v>44.23656980565704</v>
       </c>
       <c r="C6" t="n">
-        <v>171.9953255501115</v>
+        <v>148.7298684548706</v>
       </c>
       <c r="D6" t="n">
-        <v>58.24414604985053</v>
+        <v>66.5762388157932</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.33983324105218</v>
+        <v>33.53650157707104</v>
       </c>
       <c r="C7" t="n">
-        <v>171.5751375326938</v>
+        <v>144.0272969515283</v>
       </c>
       <c r="D7" t="n">
-        <v>44.25620475974196</v>
+        <v>45.8132566186774</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.95250056176443</v>
+        <v>19.61041039233004</v>
       </c>
       <c r="C8" t="n">
-        <v>124.5886924074415</v>
+        <v>111.1534750748239</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.7201294554942</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.64687392610741</v>
+        <v>9.873436661610169</v>
       </c>
       <c r="C9" t="n">
-        <v>70.77811898996953</v>
+        <v>69.77968157475051</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
         <v>41.42484438069417</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.833192302374364</v>
+        <v>7.8419694824251</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8523508930699</v>
+        <v>101.9456032715263</v>
       </c>
       <c r="D21" t="n">
-        <v>8.812341340171159</v>
+        <v>8.822215667728237</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.69828465962674</v>
+        <v>6.893832379221102</v>
       </c>
       <c r="C2" t="n">
-        <v>10.11887358767187</v>
+        <v>13.19763438818987</v>
       </c>
       <c r="D2" t="n">
-        <v>27.90716024091983</v>
+        <v>44.93950116189774</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.94143929511046</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="C3" t="n">
-        <v>27.01278808235099</v>
+        <v>33.25179474283947</v>
       </c>
       <c r="D3" t="n">
-        <v>77.10155595302325</v>
+        <v>88.568369138626</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.21761349964007</v>
+        <v>29.96686692442964</v>
       </c>
       <c r="C4" t="n">
-        <v>67.17019617686253</v>
+        <v>58.82337719535614</v>
       </c>
       <c r="D4" t="n">
-        <v>108.266155076634</v>
+        <v>128.7120327652781</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.74944301790137</v>
+        <v>45.0622196249286</v>
       </c>
       <c r="C5" t="n">
-        <v>113.3673161479005</v>
+        <v>109.3176068678824</v>
       </c>
       <c r="D5" t="n">
-        <v>94.2477796076938</v>
+        <v>118.2269672839222</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.4667817945363</v>
+        <v>50.59633143376788</v>
       </c>
       <c r="C6" t="n">
-        <v>174.0481599996916</v>
+        <v>162.7776963549382</v>
       </c>
       <c r="D6" t="n">
-        <v>66.89825206278616</v>
+        <v>78.81274220152547</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.58611304609789</v>
+        <v>41.3816474817073</v>
       </c>
       <c r="C7" t="n">
-        <v>202.8359479313208</v>
+        <v>174.9886743003599</v>
       </c>
       <c r="D7" t="n">
-        <v>49.58611304609789</v>
+        <v>52.64033015400972</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.96356182841841</v>
+        <v>26.70353755551324</v>
       </c>
       <c r="C8" t="n">
-        <v>167.0640068316797</v>
+        <v>144.1991027997715</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>41.14013754646259</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.9718734739421</v>
+        <v>13.7562488319063</v>
       </c>
       <c r="C9" t="n">
-        <v>106.0562409943744</v>
+        <v>98.06874167262235</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.683558444063038</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>58.36490101747288</v>
+        <v>58.79196126882024</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56010457970196</v>
+        <v>38.73780091417063</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1604,7 +1604,7 @@
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.992225774592398</v>
+        <v>8.002794062575207</v>
       </c>
       <c r="C21" t="n">
-        <v>108.8940761788214</v>
+        <v>110.0384183604091</v>
       </c>
       <c r="D21" t="n">
-        <v>9.990282218240496</v>
+        <v>10.00349257821901</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.761697349775283</v>
+        <v>6.256678119164923</v>
       </c>
       <c r="C2" t="n">
-        <v>6.961572970814132</v>
+        <v>9.079202768874502</v>
       </c>
       <c r="D2" t="n">
-        <v>23.06518056357456</v>
+        <v>36.80179444139593</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.53954463117502</v>
+        <v>20.27309009269663</v>
       </c>
       <c r="C3" t="n">
-        <v>42.50967559388689</v>
+        <v>48.65050748395069</v>
       </c>
       <c r="D3" t="n">
-        <v>83.10494316449251</v>
+        <v>95.98056430568943</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.97740410726909</v>
+        <v>21.64557338323367</v>
       </c>
       <c r="C4" t="n">
-        <v>92.69563648727959</v>
+        <v>86.74820889495241</v>
       </c>
       <c r="D4" t="n">
-        <v>104.5394407913131</v>
+        <v>126.504082178427</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.24412068765475</v>
+        <v>28.49522711576368</v>
       </c>
       <c r="C5" t="n">
-        <v>103.9916255723434</v>
+        <v>97.26665379825276</v>
       </c>
       <c r="D5" t="n">
-        <v>65.2862223324129</v>
+        <v>78.85888434362505</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.79251674370121</v>
+        <v>25.68055644768807</v>
       </c>
       <c r="C6" t="n">
-        <v>133.5952458462017</v>
+        <v>115.2404907676034</v>
       </c>
       <c r="D6" t="n">
-        <v>32.6440929139107</v>
+        <v>34.65667570761666</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.51736534460484</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="C7" t="n">
-        <v>117.4376421297077</v>
+        <v>101.3880306606808</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>28.92523261022377</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.43383467428585</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>78.10784734987622</v>
+        <v>72.26644850960771</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>44.48593372253571</v>
+        <v>44.81874619427537</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1901,7 +1901,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.535674393620264</v>
+        <v>3.744385743997335</v>
       </c>
       <c r="C2" t="n">
-        <v>4.022220344299182</v>
+        <v>3.838633523605029</v>
       </c>
       <c r="D2" t="n">
-        <v>16.06924642311179</v>
+        <v>25.57550944333366</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.52896639060656</v>
+        <v>21.4070086911017</v>
       </c>
       <c r="C3" t="n">
-        <v>35.42145716922492</v>
+        <v>42.80419990516094</v>
       </c>
       <c r="D3" t="n">
-        <v>83.49764224619122</v>
+        <v>103.3436720875405</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.45185029032756</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="C4" t="n">
-        <v>102.5356937269454</v>
+        <v>106.5814760161465</v>
       </c>
       <c r="D4" t="n">
-        <v>118.42528032018</v>
+        <v>141.5896174018835</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.74757733348411</v>
+        <v>31.41592653589794</v>
       </c>
       <c r="C5" t="n">
-        <v>136.7574552015807</v>
+        <v>127.9462695559656</v>
       </c>
       <c r="D5" t="n">
-        <v>81.48505945248527</v>
+        <v>98.49383842856128</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.26674194258143</v>
+        <v>30.63151012020474</v>
       </c>
       <c r="C6" t="n">
-        <v>152.8757890099048</v>
+        <v>136.0103451986489</v>
       </c>
       <c r="D6" t="n">
-        <v>40.33215918586747</v>
+        <v>44.67933802027235</v>
       </c>
     </row>
     <row r="7">
@@ -2094,10 +2094,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.08008670558751</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="C7" t="n">
-        <v>149.2374320179661</v>
+        <v>128.8160980219282</v>
       </c>
       <c r="D7" t="n">
         <v>31.62013005838127</v>
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>102.4748253692821</v>
+        <v>93.46238144429634</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>49.81093327037041</v>
+        <v>49.92187076095029</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06718511671205</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.335397861953915</v>
+        <v>3.249584901056942</v>
       </c>
       <c r="C2" t="n">
-        <v>4.886158324036376</v>
+        <v>5.593998418798326</v>
       </c>
       <c r="D2" t="n">
-        <v>24.39250345971625</v>
+        <v>29.14907108679205</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.94911335029519</v>
+        <v>17.04804888424586</v>
       </c>
       <c r="C3" t="n">
-        <v>24.86276061005047</v>
+        <v>28.37250865273282</v>
       </c>
       <c r="D3" t="n">
-        <v>77.45498512655212</v>
+        <v>99.73084053591224</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.35197406640165</v>
+        <v>34.90603962449534</v>
       </c>
       <c r="C4" t="n">
-        <v>96.26919813073798</v>
+        <v>106.6197641766121</v>
       </c>
       <c r="D4" t="n">
-        <v>130.9199833521292</v>
+        <v>158.0280009617921</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.22082078466008</v>
+        <v>37.08551952792327</v>
       </c>
       <c r="C5" t="n">
-        <v>161.742934274662</v>
+        <v>160.7611865704152</v>
       </c>
       <c r="D5" t="n">
-        <v>101.4636252339079</v>
+        <v>122.1785017935156</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.65417243286043</v>
+        <v>35.90447703971436</v>
       </c>
       <c r="C6" t="n">
-        <v>184.4330872152143</v>
+        <v>168.6141864566855</v>
       </c>
       <c r="D6" t="n">
-        <v>53.21268906558563</v>
+        <v>60.90075533754239</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.94330497952771</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="C7" t="n">
-        <v>182.1151808854876</v>
+        <v>159.7175887608009</v>
       </c>
       <c r="D7" t="n">
-        <v>35.15344004596554</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.77039421039326</v>
+        <v>11.59934912567606</v>
       </c>
       <c r="C8" t="n">
-        <v>145.7846253421301</v>
+        <v>128.8445687053514</v>
       </c>
       <c r="D8" t="n">
-        <v>29.70768553050848</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>82.87030546317747</v>
+        <v>78.5437433305618</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>43.13308538608361</v>
+        <v>43.2754388031994</v>
       </c>
       <c r="D10" t="n">
         <v>30.03657101143117</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2481,7 +2481,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.604576659366788</v>
+        <v>1.952696183746906</v>
       </c>
       <c r="C2" t="n">
-        <v>2.352267499375358</v>
+        <v>2.674280746368311</v>
       </c>
       <c r="D2" t="n">
-        <v>17.00387023755475</v>
+        <v>20.30057902841554</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.63986282345744</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="C3" t="n">
-        <v>23.76320318129405</v>
+        <v>27.42021337961341</v>
       </c>
       <c r="D3" t="n">
-        <v>80.34623211555896</v>
+        <v>102.2784758284327</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.37223091529233</v>
+        <v>38.39026222686728</v>
       </c>
       <c r="C4" t="n">
-        <v>94.09953570435253</v>
+        <v>104.2203727874329</v>
       </c>
       <c r="D4" t="n">
-        <v>139.8155993003095</v>
+        <v>170.1653478293954</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.67519004527711</v>
+        <v>38.58268477689965</v>
       </c>
       <c r="C5" t="n">
-        <v>191.4408023281281</v>
+        <v>193.9933463591698</v>
       </c>
       <c r="D5" t="n">
-        <v>107.1577619185394</v>
+        <v>128.8543861823939</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.73717901936489</v>
+        <v>29.38370878810704</v>
       </c>
       <c r="C6" t="n">
-        <v>222.1891404251382</v>
+        <v>202.6670873261903</v>
       </c>
       <c r="D6" t="n">
-        <v>52.16614601285853</v>
+        <v>59.04917916733292</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.761517423326035</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="C7" t="n">
-        <v>190.3196464498782</v>
+        <v>168.2813739849458</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>105.3120762345553</v>
+        <v>95.71549242554278</v>
       </c>
       <c r="D8" t="n">
         <v>31.29320807286708</v>
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.9484347022272</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2778,7 +2778,7 @@
         <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.74977750860408</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.699806186678728</v>
+        <v>3.221114217633785</v>
       </c>
       <c r="C2" t="n">
-        <v>5.907175936453058</v>
+        <v>5.295547116707295</v>
       </c>
       <c r="D2" t="n">
-        <v>15.54695664445249</v>
+        <v>17.77650568079699</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.47586989911922</v>
+        <v>11.71715885018568</v>
       </c>
       <c r="C3" t="n">
-        <v>16.33628179866693</v>
+        <v>18.9280957378785</v>
       </c>
       <c r="D3" t="n">
-        <v>76.35051895927444</v>
+        <v>96.2799973554847</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.43229745170064</v>
+        <v>34.95709050511617</v>
       </c>
       <c r="C4" t="n">
-        <v>77.83983022661685</v>
+        <v>86.8758360965045</v>
       </c>
       <c r="D4" t="n">
-        <v>146.1714339376034</v>
+        <v>179.6990997853362</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.85453107998479</v>
+        <v>46.60847225911733</v>
       </c>
       <c r="C5" t="n">
-        <v>184.6667431688251</v>
+        <v>194.6560260595364</v>
       </c>
       <c r="D5" t="n">
-        <v>127.1854150851743</v>
+        <v>153.4962535589888</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.98876847355934</v>
+        <v>38.19882142453915</v>
       </c>
       <c r="C6" t="n">
-        <v>260.2269552261808</v>
+        <v>250.486054504644</v>
       </c>
       <c r="D6" t="n">
-        <v>68.06555008313562</v>
+        <v>78.73223888977722</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.00212772632452</v>
+        <v>16.04961146902685</v>
       </c>
       <c r="C7" t="n">
-        <v>247.0322660811037</v>
+        <v>223.7363748070311</v>
       </c>
       <c r="D7" t="n">
-        <v>40.36357511240336</v>
+        <v>42.22006002113408</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>166.3129698379309</v>
+        <v>146.4522137810179</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>67.00624431025328</v>
+        <v>63.45624461169682</v>
       </c>
       <c r="D9" t="n">
         <v>32.28280975874785</v>
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
         <v>21.69662426385451</v>
@@ -3117,7 +3117,7 @@
         <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.962513660789374</v>
+        <v>2.047925711058846</v>
       </c>
       <c r="C2" t="n">
-        <v>4.524875168873549</v>
+        <v>3.84746925294325</v>
       </c>
       <c r="D2" t="n">
-        <v>11.66414447415635</v>
+        <v>12.85893143022472</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.40929098167968</v>
+        <v>11.46681318560275</v>
       </c>
       <c r="C3" t="n">
-        <v>19.49260066782042</v>
+        <v>20.0374706436774</v>
       </c>
       <c r="D3" t="n">
-        <v>72.35971454151115</v>
+        <v>91.07673452297661</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.4886169237412</v>
+        <v>30.75815557405257</v>
       </c>
       <c r="C4" t="n">
-        <v>64.19648238069892</v>
+        <v>71.90516535444488</v>
       </c>
       <c r="D4" t="n">
-        <v>151.5573018431014</v>
+        <v>184.765899686954</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.44420159733863</v>
+        <v>50.48637569089224</v>
       </c>
       <c r="C5" t="n">
-        <v>173.7202562664731</v>
+        <v>188.2746659819321</v>
       </c>
       <c r="D5" t="n">
-        <v>140.7826207889926</v>
+        <v>170.5786636128833</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.71708640139023</v>
+        <v>44.63908636439822</v>
       </c>
       <c r="C6" t="n">
-        <v>286.8332997589737</v>
+        <v>281.560332839464</v>
       </c>
       <c r="D6" t="n">
-        <v>81.38884817746909</v>
+        <v>95.03415951879551</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.08575620763474</v>
+        <v>14.3727863901733</v>
       </c>
       <c r="C7" t="n">
-        <v>294.4025745587165</v>
+        <v>273.9812405626786</v>
       </c>
       <c r="D7" t="n">
-        <v>44.79518424937346</v>
+        <v>47.37030847761284</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>212.8772634503571</v>
+        <v>185.923380230261</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>76.21405602838412</v>
+        <v>72.22030636750809</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3386,7 +3386,7 @@
         <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3414,7 +3414,7 @@
         <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.586725274241098</v>
+        <v>3.831761289675301</v>
       </c>
       <c r="C2" t="n">
-        <v>9.310895227076751</v>
+        <v>10.52924412804704</v>
       </c>
       <c r="D2" t="n">
-        <v>23.00234871050277</v>
+        <v>16.237125280538</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.670214886831083</v>
+        <v>9.297150759217294</v>
       </c>
       <c r="C3" t="n">
-        <v>18.44213062427633</v>
+        <v>17.73527227721863</v>
       </c>
       <c r="D3" t="n">
-        <v>66.04216806468294</v>
+        <v>82.02992942834224</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.71986741358695</v>
+        <v>26.44435616159208</v>
       </c>
       <c r="C4" t="n">
-        <v>57.15146085502382</v>
+        <v>62.23102347679681</v>
       </c>
       <c r="D4" t="n">
-        <v>152.208200571017</v>
+        <v>186.6292568296144</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.07604620824608</v>
+        <v>49.2837347531899</v>
       </c>
       <c r="C5" t="n">
-        <v>149.8392433606695</v>
+        <v>164.6636336947963</v>
       </c>
       <c r="D5" t="n">
-        <v>156.7360209830033</v>
+        <v>190.2136176978195</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.77370897306707</v>
+        <v>53.05168244208915</v>
       </c>
       <c r="C6" t="n">
-        <v>283.6534189449182</v>
+        <v>289.4094057349173</v>
       </c>
       <c r="D6" t="n">
-        <v>98.97882179445919</v>
+        <v>116.8505570025681</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.03933632809466</v>
+        <v>26.64954143177966</v>
       </c>
       <c r="C7" t="n">
-        <v>343.569481335101</v>
+        <v>326.3820242768521</v>
       </c>
       <c r="D7" t="n">
-        <v>53.29908286355933</v>
+        <v>57.9103518304066</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>284.476123521077</v>
+        <v>254.7684379905685</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>143.7749877915368</v>
+        <v>127.0234267139735</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>51.38958357879929</v>
+        <v>50.25075624187299</v>
       </c>
       <c r="D10" t="n">
         <v>26.1930287493049</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.276133146800611</v>
+        <v>4.457134577280519</v>
       </c>
       <c r="C2" t="n">
-        <v>9.240209392370978</v>
+        <v>9.137125883425064</v>
       </c>
       <c r="D2" t="n">
-        <v>19.57408572727291</v>
+        <v>11.37551064910779</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.313398501832985</v>
+        <v>2.766565030567512</v>
       </c>
       <c r="C2" t="n">
-        <v>5.362305960596078</v>
+        <v>6.148685871697774</v>
       </c>
       <c r="D2" t="n">
-        <v>17.11284423272615</v>
+        <v>12.080405500757</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.8966387536136</v>
+        <v>12.7430852011236</v>
       </c>
       <c r="C3" t="n">
-        <v>26.35992585902686</v>
+        <v>26.69372007847078</v>
       </c>
       <c r="D3" t="n">
-        <v>73.77343123562656</v>
+        <v>88.11676519467247</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.15526467265379</v>
+        <v>37.16504109196725</v>
       </c>
       <c r="C4" t="n">
-        <v>84.14461398328987</v>
+        <v>91.29173727020665</v>
       </c>
       <c r="D4" t="n">
-        <v>155.44993149044</v>
+        <v>190.3559711149353</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.68023765251858</v>
+        <v>30.77779052813751</v>
       </c>
       <c r="C5" t="n">
-        <v>233.6559536107409</v>
+        <v>245.9768872990384</v>
       </c>
       <c r="D5" t="n">
-        <v>142.4025045009999</v>
+        <v>171.8549356284042</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.8843180018149</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="C6" t="n">
-        <v>279.1049818311428</v>
+        <v>268.8408095832423</v>
       </c>
       <c r="D6" t="n">
-        <v>79.01400048089606</v>
+        <v>90.4052190932718</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.228207435741766</v>
+        <v>4.970588626601601</v>
       </c>
       <c r="C7" t="n">
-        <v>200.0212772632451</v>
+        <v>179.1208503875348</v>
       </c>
       <c r="D7" t="n">
-        <v>32.63820242768521</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>105.9796646734432</v>
+        <v>93.6292785540183</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>38.2734342500619</v>
       </c>
       <c r="D9" t="n">
         <v>19.96874830438012</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.310093405821751</v>
+        <v>6.203663743135595</v>
       </c>
       <c r="C2" t="n">
-        <v>5.63228657926395</v>
+        <v>5.737333583618359</v>
       </c>
       <c r="D2" t="n">
-        <v>18.01016163440774</v>
+        <v>30.63445536331747</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.57328390601791</v>
+        <v>9.47386534598172</v>
       </c>
       <c r="C3" t="n">
-        <v>23.28214680621311</v>
+        <v>23.0219836645877</v>
       </c>
       <c r="D3" t="n">
-        <v>19.5760492226814</v>
+        <v>12.68908907739002</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4585,7 +4585,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
         <v>32.21899615797182</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.930157044278233</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
         <v>27.36523550817559</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39564164384284</v>
+        <v>13.39771539668841</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13012390011841</v>
+        <v>70.14098060619227</v>
       </c>
       <c r="D21" t="n">
-        <v>1.575957840452099</v>
+        <v>1.576201811375107</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.603414985213294</v>
+        <v>4.667228585989336</v>
       </c>
       <c r="C2" t="n">
-        <v>8.683558444063037</v>
+        <v>4.62599518241097</v>
       </c>
       <c r="D2" t="n">
-        <v>16.38438743617502</v>
+        <v>23.91930106626929</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.24640297823272</v>
+        <v>16.6062624173348</v>
       </c>
       <c r="C3" t="n">
-        <v>22.45747873464579</v>
+        <v>22.61455836732528</v>
       </c>
       <c r="D3" t="n">
-        <v>29.97275741065512</v>
+        <v>35.35273482992764</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.27996232662636</v>
+        <v>11.12909197534184</v>
       </c>
       <c r="C4" t="n">
-        <v>36.02915899815369</v>
+        <v>35.63351467334223</v>
       </c>
       <c r="D4" t="n">
-        <v>25.33399950808894</v>
+        <v>21.72214970416493</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.58368222013712</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4896,7 +4896,7 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4910,10 +4910,10 @@
         <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45180923259856</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.04843409934012</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43429172289843</v>
+        <v>15.4372312724469</v>
       </c>
       <c r="C21" t="n">
-        <v>86.10710119090706</v>
+        <v>86.12350078312483</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249324573241775</v>
+        <v>3.249943425778295</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.857687640613218</v>
+        <v>4.742823159216341</v>
       </c>
       <c r="C2" t="n">
-        <v>10.26220875249191</v>
+        <v>6.980226177194822</v>
       </c>
       <c r="D2" t="n">
-        <v>14.12440422099886</v>
+        <v>38.05450451201487</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.87409961414493</v>
+        <v>16.3608254912731</v>
       </c>
       <c r="C3" t="n">
-        <v>29.19717672430014</v>
+        <v>19.84602984134927</v>
       </c>
       <c r="D3" t="n">
-        <v>36.12340677776139</v>
+        <v>46.28449551671588</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.80019079888594</v>
+        <v>23.04947260030661</v>
       </c>
       <c r="C4" t="n">
-        <v>47.71981066032471</v>
+        <v>47.43903081691013</v>
       </c>
       <c r="D4" t="n">
-        <v>34.65078522139117</v>
+        <v>34.53592073999429</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.15604113171301</v>
+        <v>10.08745766113598</v>
       </c>
       <c r="C5" t="n">
-        <v>39.61351986635881</v>
+        <v>39.85895679242051</v>
       </c>
       <c r="D5" t="n">
-        <v>31.73499453977815</v>
+        <v>30.48326621686347</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.39751000922872</v>
+        <v>12.31700669748049</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.37385025333556</v>
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.2069942013426</v>
+        <v>29.37389131106456</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.04687151455913</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>48.82722207071512</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72165752570044</v>
+        <v>16.72653281085917</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0021109067727</v>
+        <v>102.0318501462409</v>
       </c>
       <c r="D21" t="n">
-        <v>4.18041438142511</v>
+        <v>4.181633202714792</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.324999547834699</v>
+        <v>4.602433237509047</v>
       </c>
       <c r="C2" t="n">
-        <v>8.285950623843078</v>
+        <v>8.926050127011999</v>
       </c>
       <c r="D2" t="n">
-        <v>24.39839394594173</v>
+        <v>28.57376693210342</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.61746255270901</v>
+        <v>16.25283324380595</v>
       </c>
       <c r="C3" t="n">
-        <v>35.18583772020568</v>
+        <v>23.92519155249477</v>
       </c>
       <c r="D3" t="n">
-        <v>38.82321296444012</v>
+        <v>64.90824946627787</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.59973434077034</v>
+        <v>27.46537377400877</v>
       </c>
       <c r="C4" t="n">
-        <v>61.14619226360409</v>
+        <v>48.19203130606743</v>
       </c>
       <c r="D4" t="n">
-        <v>44.4015034199705</v>
+        <v>49.13647259755286</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.20761609614836</v>
+        <v>22.2856728864026</v>
       </c>
       <c r="C5" t="n">
-        <v>65.82618356974865</v>
+        <v>65.65437772150545</v>
       </c>
       <c r="D5" t="n">
-        <v>36.49647090537518</v>
+        <v>35.46563581591603</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.32958949118645</v>
+        <v>9.740900721536855</v>
       </c>
       <c r="C6" t="n">
-        <v>38.48058301565798</v>
+        <v>38.64158963915446</v>
       </c>
       <c r="D6" t="n">
-        <v>38.68184129502858</v>
+        <v>38.35982804803563</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
         <v>39.88448223273092</v>
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>48.40016181936776</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
         <v>34.28066633689012</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.74489413227862</v>
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03910716173301</v>
+        <v>18.04394012493474</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6836991027344</v>
+        <v>117.7152284340981</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013035720577669</v>
+        <v>6.014646708311579</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.499750639190632</v>
+        <v>6.010259445398973</v>
       </c>
       <c r="C2" t="n">
-        <v>5.370159942230052</v>
+        <v>8.551022503989719</v>
       </c>
       <c r="D2" t="n">
-        <v>26.46595461108551</v>
+        <v>24.005694864243</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.90431280879833</v>
+        <v>14.3286077434822</v>
       </c>
       <c r="C3" t="n">
-        <v>31.4110177973767</v>
+        <v>28.11725424962865</v>
       </c>
       <c r="D3" t="n">
-        <v>45.84270904980481</v>
+        <v>67.91730617979435</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.68310078017331</v>
+        <v>21.35203081966388</v>
       </c>
       <c r="C4" t="n">
-        <v>63.45624461169684</v>
+        <v>45.26936839052468</v>
       </c>
       <c r="D4" t="n">
-        <v>46.5073522455799</v>
+        <v>60.63568345739575</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.96722677732814</v>
+        <v>19.315886081056</v>
       </c>
       <c r="C5" t="n">
-        <v>66.80793127399546</v>
+        <v>58.09492039880502</v>
       </c>
       <c r="D5" t="n">
-        <v>35.22019888985433</v>
+        <v>35.83379120500859</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.18116566139593</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>49.02651685467723</v>
+        <v>48.98626519880311</v>
       </c>
       <c r="D6" t="n">
-        <v>32.16107304342126</v>
+        <v>31.75855648468008</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.347980655659875</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>24.43373686329462</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>31.32069700858599</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.63281066307846</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
         <v>30.17499743772996</v>
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>32.88363935374691</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5955,7 +5955,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.046203873394346</v>
+        <v>7.049039941165295</v>
       </c>
       <c r="C21" t="n">
-        <v>66.05816131307199</v>
+        <v>66.08474944842463</v>
       </c>
       <c r="D21" t="n">
-        <v>4.403877420871466</v>
+        <v>4.405649963228309</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.587707021945345</v>
+        <v>5.303401098341269</v>
       </c>
       <c r="C2" t="n">
-        <v>3.604977569994288</v>
+        <v>4.748713645441821</v>
       </c>
       <c r="D2" t="n">
-        <v>24.72924292227291</v>
+        <v>19.95696733192916</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.94143929511046</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="C3" t="n">
-        <v>24.77440331666826</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D3" t="n">
-        <v>56.99536297004857</v>
+        <v>71.6724911485384</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.83098483061608</v>
+        <v>25.58925391119311</v>
       </c>
       <c r="C4" t="n">
-        <v>72.96447112732719</v>
+        <v>60.45700537522283</v>
       </c>
       <c r="D4" t="n">
-        <v>59.74229304653115</v>
+        <v>82.16639235923255</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.44676162535709</v>
+        <v>26.5808190924824</v>
       </c>
       <c r="C5" t="n">
-        <v>96.57943040527999</v>
+        <v>73.82742735936016</v>
       </c>
       <c r="D5" t="n">
-        <v>44.20319038371264</v>
+        <v>49.89732706834415</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.16986771503048</v>
+        <v>19.68305972244431</v>
       </c>
       <c r="C6" t="n">
-        <v>82.71715282131501</v>
+        <v>74.58631833474294</v>
       </c>
       <c r="D6" t="n">
-        <v>36.58875518957439</v>
+        <v>36.46800022195202</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.65414707066464</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>51.50248456478767</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>26.8704346652352</v>
+        <v>26.95388322009618</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6308,7 +6308,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.264072522773835</v>
+        <v>7.267694172732917</v>
       </c>
       <c r="C21" t="n">
-        <v>75.36475242377854</v>
+        <v>75.40232704210402</v>
       </c>
       <c r="D21" t="n">
-        <v>5.448054392080376</v>
+        <v>5.450770629549688</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.938190952361456</v>
+        <v>3.818998569520092</v>
       </c>
       <c r="C2" t="n">
-        <v>10.56458704539993</v>
+        <v>4.221515128261284</v>
       </c>
       <c r="D2" t="n">
-        <v>23.16826407252048</v>
+        <v>23.15844659547801</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.75352457297182</v>
+        <v>18.31450342272425</v>
       </c>
       <c r="C3" t="n">
-        <v>18.34886459237289</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D3" t="n">
-        <v>63.55343763441726</v>
+        <v>71.0098114481718</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.08547847019426</v>
+        <v>31.06446085777758</v>
       </c>
       <c r="C4" t="n">
-        <v>66.6852128109646</v>
+        <v>71.07558854435634</v>
       </c>
       <c r="D4" t="n">
-        <v>74.90440459091889</v>
+        <v>99.66408169202344</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.68085954732433</v>
+        <v>33.20761609614836</v>
       </c>
       <c r="C5" t="n">
-        <v>118.0797051282851</v>
+        <v>94.39504176333082</v>
       </c>
       <c r="D5" t="n">
-        <v>55.73872590861267</v>
+        <v>68.08420328951631</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.14598697495907</v>
+        <v>28.29691407950582</v>
       </c>
       <c r="C6" t="n">
-        <v>120.19144444012</v>
+        <v>98.25429198872504</v>
       </c>
       <c r="D6" t="n">
-        <v>41.90197376495812</v>
+        <v>43.43153668817465</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.71509754378595</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="C7" t="n">
-        <v>88.63218273940203</v>
+        <v>82.34408869370121</v>
       </c>
       <c r="D7" t="n">
-        <v>37.00992495469625</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>49.23464736797754</v>
+        <v>49.31809592283852</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>29.17656002251095</v>
+        <v>28.95468504135117</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.468695218880244</v>
+        <v>7.473766300294549</v>
       </c>
       <c r="C21" t="n">
-        <v>84.02282121240275</v>
+        <v>85.01409166585049</v>
       </c>
       <c r="D21" t="n">
-        <v>6.535108316520214</v>
+        <v>6.53954551275773</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_61_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_61_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497627541351</v>
+        <v>10.84497615180899</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907174398579</v>
+        <v>37.78907131328867</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.963716392671873</v>
+        <v>6.270422587024377</v>
       </c>
       <c r="C2" t="n">
-        <v>7.853981633974483</v>
+        <v>6.160466844148735</v>
       </c>
       <c r="D2" t="n">
-        <v>36.69969268015426</v>
+        <v>33.17227317879548</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.45270886484479</v>
+        <v>20.65597169735289</v>
       </c>
       <c r="C3" t="n">
-        <v>19.58095796120263</v>
+        <v>26.51209675318512</v>
       </c>
       <c r="D3" t="n">
-        <v>72.57079029792423</v>
+        <v>71.50559403881644</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.3362250454047</v>
+        <v>35.35273482992764</v>
       </c>
       <c r="C4" t="n">
-        <v>64.69422846675207</v>
+        <v>46.30314872309656</v>
       </c>
       <c r="D4" t="n">
-        <v>110.346478461933</v>
+        <v>95.49067220127026</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.66260725157115</v>
+        <v>44.47317100238052</v>
       </c>
       <c r="C5" t="n">
-        <v>113.5391219961436</v>
+        <v>75.69274799742909</v>
       </c>
       <c r="D5" t="n">
-        <v>87.35100198535997</v>
+        <v>67.07791189266334</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.79001346894498</v>
+        <v>42.2642386678252</v>
       </c>
       <c r="C6" t="n">
-        <v>123.4115769100496</v>
+        <v>109.6857622569749</v>
       </c>
       <c r="D6" t="n">
-        <v>53.53470231257858</v>
+        <v>47.0944373727195</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.09248957284423</v>
+        <v>28.68568617038755</v>
       </c>
       <c r="C7" t="n">
-        <v>112.9461463827785</v>
+        <v>115.2817241711817</v>
       </c>
       <c r="D7" t="n">
-        <v>40.96244121199391</v>
+        <v>38.92629647338602</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.18487166803466</v>
+        <v>14.01935721664445</v>
       </c>
       <c r="C8" t="n">
-        <v>78.94233289848603</v>
+        <v>83.11476064153496</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>45.37343364717482</v>
+        <v>46.14999608123405</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
         <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.66572128392411</v>
+        <v>7.687964943231894</v>
       </c>
       <c r="C21" t="n">
-        <v>93.90508572807033</v>
+        <v>93.21657493668671</v>
       </c>
       <c r="D21" t="n">
-        <v>7.66572128392411</v>
+        <v>7.687964943231894</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.440845776935824</v>
+        <v>7.149086782325274</v>
       </c>
       <c r="C2" t="n">
-        <v>11.14578168631404</v>
+        <v>6.595381077130072</v>
       </c>
       <c r="D2" t="n">
-        <v>35.03955731227291</v>
+        <v>30.74637460160161</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.90431280879833</v>
+        <v>20.73942025221387</v>
       </c>
       <c r="C3" t="n">
-        <v>24.98057033456009</v>
+        <v>25.03456645829367</v>
       </c>
       <c r="D3" t="n">
-        <v>82.77605768356982</v>
+        <v>79.53138152103412</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.06446085777758</v>
+        <v>36.98636300979434</v>
       </c>
       <c r="C4" t="n">
-        <v>56.23254500384881</v>
+        <v>56.41122308602172</v>
       </c>
       <c r="D4" t="n">
-        <v>119.7653659364769</v>
+        <v>106.4155606541288</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.54680208019903</v>
+        <v>48.79286090106649</v>
       </c>
       <c r="C5" t="n">
-        <v>116.1652971050039</v>
+        <v>79.66882619962867</v>
       </c>
       <c r="D5" t="n">
-        <v>103.0344215607028</v>
+        <v>84.03760348352698</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.23656980565704</v>
+        <v>50.47557646614552</v>
       </c>
       <c r="C6" t="n">
-        <v>148.7298684548706</v>
+        <v>115.2404907676034</v>
       </c>
       <c r="D6" t="n">
-        <v>66.5762388157932</v>
+        <v>55.62778841803278</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.53650157707104</v>
+        <v>38.74663664350886</v>
       </c>
       <c r="C7" t="n">
-        <v>144.0272969515283</v>
+        <v>136.7810171464826</v>
       </c>
       <c r="D7" t="n">
-        <v>45.8132566186774</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.61041039233004</v>
+        <v>22.03041848329842</v>
       </c>
       <c r="C8" t="n">
-        <v>111.1534750748239</v>
+        <v>115.6596970373167</v>
       </c>
       <c r="D8" t="n">
-        <v>38.7201294554942</v>
+        <v>37.80219535202343</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>10.31718662392973</v>
       </c>
       <c r="C9" t="n">
-        <v>69.77968157475051</v>
+        <v>73.21874378272709</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>41.42484438069417</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.8419694824251</v>
+        <v>7.870858954790839</v>
       </c>
       <c r="C21" t="n">
-        <v>101.9456032715263</v>
+        <v>101.337309042932</v>
       </c>
       <c r="D21" t="n">
-        <v>8.822215667728237</v>
+        <v>8.854716324139694</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.893832379221102</v>
+        <v>8.347800729210629</v>
       </c>
       <c r="C2" t="n">
-        <v>13.19763438818987</v>
+        <v>7.403359437725197</v>
       </c>
       <c r="D2" t="n">
-        <v>44.93950116189774</v>
+        <v>32.59991426721958</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.58662746324986</v>
+        <v>21.92733497435251</v>
       </c>
       <c r="C3" t="n">
-        <v>33.25179474283947</v>
+        <v>25.11310627463341</v>
       </c>
       <c r="D3" t="n">
-        <v>88.568369138626</v>
+        <v>83.80689277302896</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.96686692442964</v>
+        <v>37.76488893926206</v>
       </c>
       <c r="C4" t="n">
-        <v>58.82337719535614</v>
+        <v>58.51707191163113</v>
       </c>
       <c r="D4" t="n">
-        <v>128.7120327652781</v>
+        <v>118.5911956821977</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.0622196249286</v>
+        <v>51.27177385428968</v>
       </c>
       <c r="C5" t="n">
-        <v>109.3176068678824</v>
+        <v>89.68265278294614</v>
       </c>
       <c r="D5" t="n">
-        <v>118.2269672839222</v>
+        <v>98.02750826904405</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.59633143376788</v>
+        <v>56.91584140600459</v>
       </c>
       <c r="C6" t="n">
-        <v>162.7776963549382</v>
+        <v>120.6744643106095</v>
       </c>
       <c r="D6" t="n">
-        <v>78.81274220152547</v>
+        <v>66.69699378341556</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.3816474817073</v>
+        <v>47.90928796724435</v>
       </c>
       <c r="C7" t="n">
-        <v>174.9886743003599</v>
+        <v>149.6566382876795</v>
       </c>
       <c r="D7" t="n">
-        <v>52.64033015400972</v>
+        <v>47.84940135728529</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.70353755551324</v>
+        <v>30.54217107911827</v>
       </c>
       <c r="C8" t="n">
-        <v>144.1991027997715</v>
+        <v>145.7011767872691</v>
       </c>
       <c r="D8" t="n">
-        <v>41.14013754646259</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.7562488319063</v>
+        <v>15.42031119060464</v>
       </c>
       <c r="C9" t="n">
-        <v>98.06874167262235</v>
+        <v>103.1718662392973</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>58.79196126882024</v>
+        <v>60.78490910844128</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73780091417063</v>
+        <v>40.15937158992001</v>
       </c>
       <c r="D11" t="n">
         <v>36.42774856607789</v>
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
         <v>35.79943003535993</v>
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.002794062575207</v>
+        <v>8.03911620179511</v>
       </c>
       <c r="C21" t="n">
-        <v>110.0384183604091</v>
+        <v>109.5329582494584</v>
       </c>
       <c r="D21" t="n">
-        <v>10.00349257821901</v>
+        <v>10.04889525224389</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.256678119164923</v>
+        <v>7.621307428067988</v>
       </c>
       <c r="C2" t="n">
-        <v>9.079202768874502</v>
+        <v>4.974515617418588</v>
       </c>
       <c r="D2" t="n">
-        <v>36.80179444139593</v>
+        <v>26.72317250959818</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.27309009269663</v>
+        <v>26.38446955163303</v>
       </c>
       <c r="C3" t="n">
-        <v>48.65050748395069</v>
+        <v>37.70402058159875</v>
       </c>
       <c r="D3" t="n">
-        <v>95.98056430568943</v>
+        <v>90.80675390430872</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.64557338323367</v>
+        <v>24.63204989955247</v>
       </c>
       <c r="C4" t="n">
-        <v>86.74820889495241</v>
+        <v>77.9036438273929</v>
       </c>
       <c r="D4" t="n">
-        <v>126.504082178427</v>
+        <v>113.2946668177862</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.49522711576368</v>
+        <v>32.05406254365837</v>
       </c>
       <c r="C5" t="n">
-        <v>97.26665379825276</v>
+        <v>72.10936887692823</v>
       </c>
       <c r="D5" t="n">
-        <v>78.85888434362505</v>
+        <v>67.12699927787567</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.68055644768807</v>
+        <v>29.74597369097411</v>
       </c>
       <c r="C6" t="n">
-        <v>115.2404907676034</v>
+        <v>98.576305235718</v>
       </c>
       <c r="D6" t="n">
-        <v>34.65667570761666</v>
+        <v>31.51704654943536</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.66654993792135</v>
+        <v>20.24167416616073</v>
       </c>
       <c r="C7" t="n">
-        <v>101.3880306606808</v>
+        <v>102.4659896399438</v>
       </c>
       <c r="D7" t="n">
-        <v>28.92523261022377</v>
+        <v>28.44613973055133</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>72.26644850960771</v>
+        <v>76.02163347835176</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>44.81874619427537</v>
+        <v>46.37187106239383</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
         <v>28.47068342315751</v>
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>28.60910984945629</v>
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.744385743997335</v>
+        <v>4.560218086226434</v>
       </c>
       <c r="C2" t="n">
-        <v>3.838633523605029</v>
+        <v>2.358157985600839</v>
       </c>
       <c r="D2" t="n">
-        <v>25.57550944333366</v>
+        <v>19.24912723716721</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.4070086911017</v>
+        <v>27.10605411425443</v>
       </c>
       <c r="C3" t="n">
-        <v>42.80419990516094</v>
+        <v>28.80447764260142</v>
       </c>
       <c r="D3" t="n">
-        <v>103.3436720875405</v>
+        <v>91.39580252685681</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.27768003604838</v>
+        <v>35.97810811753286</v>
       </c>
       <c r="C4" t="n">
-        <v>106.5814760161465</v>
+        <v>87.98619275000765</v>
       </c>
       <c r="D4" t="n">
-        <v>141.5896174018835</v>
+        <v>130.8816951916635</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.41592653589794</v>
+        <v>35.95650966803944</v>
       </c>
       <c r="C5" t="n">
-        <v>127.9462695559656</v>
+        <v>106.8877812998715</v>
       </c>
       <c r="D5" t="n">
-        <v>98.49383842856128</v>
+        <v>85.16661334341082</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.63151012020474</v>
+        <v>35.66296710446964</v>
       </c>
       <c r="C6" t="n">
-        <v>136.0103451986489</v>
+        <v>111.5373384271844</v>
       </c>
       <c r="D6" t="n">
-        <v>44.67933802027235</v>
+        <v>39.56737772425921</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.46881773874025</v>
+        <v>18.92416874706152</v>
       </c>
       <c r="C7" t="n">
-        <v>128.8160980219282</v>
+        <v>122.5280039762274</v>
       </c>
       <c r="D7" t="n">
-        <v>31.62013005838127</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.094509821514951</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>93.46238144429634</v>
+        <v>99.05343461998193</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>28.37250865273282</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>49.92187076095029</v>
+        <v>52.91718300660731</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
         <v>29.75186417719959</v>
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.249584901056942</v>
+        <v>4.645630136495907</v>
       </c>
       <c r="C2" t="n">
-        <v>5.593998418798326</v>
+        <v>5.731443097392879</v>
       </c>
       <c r="D2" t="n">
-        <v>29.14907108679205</v>
+        <v>18.30174070256904</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.04804888424586</v>
+        <v>21.23520284285851</v>
       </c>
       <c r="C3" t="n">
-        <v>28.37250865273282</v>
+        <v>18.27032477603314</v>
       </c>
       <c r="D3" t="n">
-        <v>99.73084053591224</v>
+        <v>85.80474935117122</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.90603962449534</v>
+        <v>43.61021477034756</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6197641766121</v>
+        <v>79.61384832819084</v>
       </c>
       <c r="D4" t="n">
-        <v>158.0280009617921</v>
+        <v>145.3418571275148</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.08551952792327</v>
+        <v>44.49771469498668</v>
       </c>
       <c r="C5" t="n">
-        <v>160.7611865704152</v>
+        <v>134.5730665596316</v>
       </c>
       <c r="D5" t="n">
-        <v>122.1785017935156</v>
+        <v>109.7348496421873</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.90447703971436</v>
+        <v>42.22398701195107</v>
       </c>
       <c r="C6" t="n">
-        <v>168.6141864566855</v>
+        <v>140.8807955594173</v>
       </c>
       <c r="D6" t="n">
-        <v>60.90075533754239</v>
+        <v>54.37998708593508</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.37385025333556</v>
+        <v>28.56591295046944</v>
       </c>
       <c r="C7" t="n">
-        <v>159.7175887608009</v>
+        <v>142.7696781423882</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.59934912567606</v>
+        <v>13.18487166803466</v>
       </c>
       <c r="C8" t="n">
-        <v>128.8445687053514</v>
+        <v>129.4287085893783</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>78.5437433305618</v>
+        <v>83.42499291607693</v>
       </c>
       <c r="D9" t="n">
         <v>29.28749751309084</v>
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>43.2754388031994</v>
+        <v>46.12250714551515</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.952696183746906</v>
+        <v>2.731222113214627</v>
       </c>
       <c r="C2" t="n">
-        <v>2.674280746368311</v>
+        <v>2.642864819832413</v>
       </c>
       <c r="D2" t="n">
-        <v>20.30057902841554</v>
+        <v>12.63509295365645</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.27246819789088</v>
+        <v>20.95049600862693</v>
       </c>
       <c r="C3" t="n">
-        <v>27.42021337961341</v>
+        <v>21.25483779694344</v>
       </c>
       <c r="D3" t="n">
-        <v>102.2784758284327</v>
+        <v>84.38121518001336</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.39026222686728</v>
+        <v>48.26860762699868</v>
       </c>
       <c r="C4" t="n">
-        <v>104.2203727874329</v>
+        <v>74.80230282967722</v>
       </c>
       <c r="D4" t="n">
-        <v>170.1653478293954</v>
+        <v>155.3605924493535</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.58268477689965</v>
+        <v>46.38757902566179</v>
       </c>
       <c r="C5" t="n">
-        <v>193.9933463591698</v>
+        <v>157.3005259129452</v>
       </c>
       <c r="D5" t="n">
-        <v>128.8543861823939</v>
+        <v>119.65050145508</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.38370878810704</v>
+        <v>35.26045054572845</v>
       </c>
       <c r="C6" t="n">
-        <v>202.6670873261903</v>
+        <v>176.5035110080129</v>
       </c>
       <c r="D6" t="n">
-        <v>59.04917916733292</v>
+        <v>52.89067581859268</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.665486074759095</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>168.2813739849458</v>
+        <v>158.4000833417016</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>35.09355343600648</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>95.71549242554278</v>
+        <v>102.0575825949772</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>32.9484347022272</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.221114217633785</v>
+        <v>3.650137964389641</v>
       </c>
       <c r="C2" t="n">
-        <v>5.295547116707295</v>
+        <v>4.063453747877548</v>
       </c>
       <c r="D2" t="n">
-        <v>17.77650568079699</v>
+        <v>14.49550485320415</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.71715885018568</v>
+        <v>15.29562923216531</v>
       </c>
       <c r="C3" t="n">
-        <v>18.9280957378785</v>
+        <v>15.38889526406875</v>
       </c>
       <c r="D3" t="n">
-        <v>96.2799973554847</v>
+        <v>75.82528393750241</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.95709050511617</v>
+        <v>44.46531702074653</v>
       </c>
       <c r="C4" t="n">
-        <v>86.8758360965045</v>
+        <v>64.38792318302706</v>
       </c>
       <c r="D4" t="n">
-        <v>179.6990997853362</v>
+        <v>161.0782910788869</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.60847225911733</v>
+        <v>57.97220193577417</v>
       </c>
       <c r="C5" t="n">
-        <v>194.6560260595364</v>
+        <v>149.3238258159399</v>
       </c>
       <c r="D5" t="n">
-        <v>153.4962535589888</v>
+        <v>143.5069706682775</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.19882142453915</v>
+        <v>46.65166915810419</v>
       </c>
       <c r="C6" t="n">
-        <v>250.486054504644</v>
+        <v>211.7639615537413</v>
       </c>
       <c r="D6" t="n">
-        <v>78.73223888977722</v>
+        <v>73.33851700264525</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.04961146902685</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="C7" t="n">
-        <v>223.7363748070311</v>
+        <v>204.2732265703381</v>
       </c>
       <c r="D7" t="n">
-        <v>42.22006002113408</v>
+        <v>40.24380189248525</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>146.4522137810179</v>
+        <v>148.2046334330985</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>63.45624461169682</v>
+        <v>69.66874408417063</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>24.52209415667683</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.047925711058846</v>
+        <v>2.66544501703009</v>
       </c>
       <c r="C2" t="n">
-        <v>3.84746925294325</v>
+        <v>2.641883072128167</v>
       </c>
       <c r="D2" t="n">
-        <v>12.85893143022472</v>
+        <v>10.44972256400305</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.46681318560275</v>
+        <v>14.24515918862122</v>
       </c>
       <c r="C3" t="n">
-        <v>20.0374706436774</v>
+        <v>15.74723317611884</v>
       </c>
       <c r="D3" t="n">
-        <v>91.07673452297661</v>
+        <v>71.29451828240336</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.75815557405257</v>
+        <v>39.28365263773187</v>
       </c>
       <c r="C4" t="n">
-        <v>71.90516535444488</v>
+        <v>54.59891682398212</v>
       </c>
       <c r="D4" t="n">
-        <v>184.765899686954</v>
+        <v>162.5715293370463</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.48637569089224</v>
+        <v>63.54362015737481</v>
       </c>
       <c r="C5" t="n">
-        <v>188.2746659819321</v>
+        <v>142.4025045009999</v>
       </c>
       <c r="D5" t="n">
-        <v>170.5786636128833</v>
+        <v>161.0311671890831</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.63908636439822</v>
+        <v>55.38627848278806</v>
       </c>
       <c r="C6" t="n">
-        <v>281.560332839464</v>
+        <v>231.1250080291927</v>
       </c>
       <c r="D6" t="n">
-        <v>95.03415951879551</v>
+        <v>87.86936477320229</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.3727863901733</v>
+        <v>19.28348840681585</v>
       </c>
       <c r="C7" t="n">
-        <v>273.9812405626786</v>
+        <v>246.4333999815131</v>
       </c>
       <c r="D7" t="n">
-        <v>47.37030847761284</v>
+        <v>45.51382356888213</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>185.923380230261</v>
+        <v>185.4226889010951</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>72.22030636750809</v>
+        <v>82.98124295375739</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.831761289675301</v>
+        <v>3.712969817461437</v>
       </c>
       <c r="C2" t="n">
-        <v>10.52924412804704</v>
+        <v>9.352128630655116</v>
       </c>
       <c r="D2" t="n">
-        <v>16.237125280538</v>
+        <v>20.49300157844792</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.297150759217294</v>
+        <v>11.69752389610075</v>
       </c>
       <c r="C3" t="n">
-        <v>17.73527227721863</v>
+        <v>13.02288329683394</v>
       </c>
       <c r="D3" t="n">
-        <v>82.02992942834224</v>
+        <v>64.86407081958676</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.44435616159208</v>
+        <v>33.42556408649115</v>
       </c>
       <c r="C4" t="n">
-        <v>62.23102347679681</v>
+        <v>47.42626809675492</v>
       </c>
       <c r="D4" t="n">
-        <v>186.6292568296144</v>
+        <v>159.3425611377786</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.2837347531899</v>
+        <v>62.43915399009715</v>
       </c>
       <c r="C5" t="n">
-        <v>164.6636336947963</v>
+        <v>123.6265796572796</v>
       </c>
       <c r="D5" t="n">
-        <v>190.2136176978195</v>
+        <v>177.9663150873406</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.05168244208915</v>
+        <v>66.61649047166733</v>
       </c>
       <c r="C6" t="n">
-        <v>289.4094057349173</v>
+        <v>230.0382133205914</v>
       </c>
       <c r="D6" t="n">
-        <v>116.8505570025681</v>
+        <v>110.4102920627091</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.64954143177966</v>
+        <v>35.99185258539232</v>
       </c>
       <c r="C7" t="n">
-        <v>326.3820242768521</v>
+        <v>286.9167483138345</v>
       </c>
       <c r="D7" t="n">
-        <v>57.9103518304066</v>
+        <v>55.87420709179872</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>254.7684379905685</v>
+        <v>242.5849489808656</v>
       </c>
       <c r="D8" t="n">
-        <v>37.46840113257952</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>127.0234267139735</v>
+        <v>139.7812381306608</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>50.25075624187299</v>
+        <v>56.65666001208344</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>27.3318560862312</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.98419422574081</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.67690719431156</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.457134577280519</v>
+        <v>4.558254590817941</v>
       </c>
       <c r="C2" t="n">
-        <v>9.137125883425064</v>
+        <v>8.06113039957056</v>
       </c>
       <c r="D2" t="n">
-        <v>11.37551064910779</v>
+        <v>4.53076565509903</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.766565030567512</v>
+        <v>2.629120351972958</v>
       </c>
       <c r="C2" t="n">
-        <v>6.148685871697774</v>
+        <v>5.236642254452487</v>
       </c>
       <c r="D2" t="n">
-        <v>12.080405500757</v>
+        <v>15.08357172804799</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.7430852011236</v>
+        <v>15.68832831386403</v>
       </c>
       <c r="C3" t="n">
-        <v>26.69372007847078</v>
+        <v>22.22185928562655</v>
       </c>
       <c r="D3" t="n">
-        <v>88.11676519467247</v>
+        <v>72.35480580298993</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.16504109196725</v>
+        <v>47.01786105178824</v>
       </c>
       <c r="C4" t="n">
-        <v>91.29173727020665</v>
+        <v>68.54856995362505</v>
       </c>
       <c r="D4" t="n">
-        <v>190.3559711149353</v>
+        <v>165.1113106479328</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.77779052813751</v>
+        <v>39.83441309981433</v>
       </c>
       <c r="C5" t="n">
-        <v>245.9768872990384</v>
+        <v>190.4835983164874</v>
       </c>
       <c r="D5" t="n">
-        <v>171.8549356284042</v>
+        <v>162.8228567493335</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.54343056426301</v>
+        <v>22.33966901013618</v>
       </c>
       <c r="C6" t="n">
-        <v>268.8408095832423</v>
+        <v>236.317471636954</v>
       </c>
       <c r="D6" t="n">
-        <v>90.4052190932718</v>
+        <v>85.73602701187396</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.970588626601601</v>
+        <v>6.467753875577986</v>
       </c>
       <c r="C7" t="n">
-        <v>179.1208503875348</v>
+        <v>170.5570651633899</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>34.6743471662931</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>93.6292785540183</v>
+        <v>102.9755166984479</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>24.86766934857171</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>38.2734342500619</v>
+        <v>43.26562132615692</v>
       </c>
       <c r="D9" t="n">
-        <v>19.96874830438012</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>23.06125357275758</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.886199381765381</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.626036240139976</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.203663743135595</v>
+        <v>6.424556976591127</v>
       </c>
       <c r="C2" t="n">
-        <v>5.737333583618359</v>
+        <v>7.872634840355172</v>
       </c>
       <c r="D2" t="n">
-        <v>30.63445536331747</v>
+        <v>22.31807056064274</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.47386534598172</v>
+        <v>9.689849840916018</v>
       </c>
       <c r="C3" t="n">
-        <v>23.0219836645877</v>
+        <v>20.63633674326795</v>
       </c>
       <c r="D3" t="n">
-        <v>12.68908907739002</v>
+        <v>6.940956269024949</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39771539668841</v>
+        <v>13.39905899333275</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14098060619227</v>
+        <v>70.14801472980088</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576201811375107</v>
+        <v>1.576359881568559</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.667228585989336</v>
+        <v>5.998478472948011</v>
       </c>
       <c r="C2" t="n">
-        <v>4.62599518241097</v>
+        <v>4.330489123432681</v>
       </c>
       <c r="D2" t="n">
-        <v>23.91930106626929</v>
+        <v>23.75044046113884</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.6062624173348</v>
+        <v>17.15113239319178</v>
       </c>
       <c r="C3" t="n">
-        <v>22.61455836732528</v>
+        <v>26.93424826601124</v>
       </c>
       <c r="D3" t="n">
-        <v>35.35273482992764</v>
+        <v>24.00864010735575</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.12909197534184</v>
+        <v>11.38434637844601</v>
       </c>
       <c r="C4" t="n">
-        <v>35.63351467334223</v>
+        <v>31.98337670895259</v>
       </c>
       <c r="D4" t="n">
-        <v>21.72214970416493</v>
+        <v>18.71014774753571</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4994,7 +4994,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4372312724469</v>
+        <v>15.4413483342185</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12350078312483</v>
+        <v>86.14646965406112</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249943425778295</v>
+        <v>3.250810175624948</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.742823159216341</v>
+        <v>5.602834148136546</v>
       </c>
       <c r="C2" t="n">
-        <v>6.980226177194822</v>
+        <v>4.351105825221864</v>
       </c>
       <c r="D2" t="n">
-        <v>38.05450451201487</v>
+        <v>21.09481292115122</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.3608254912731</v>
+        <v>19.20789383358884</v>
       </c>
       <c r="C3" t="n">
-        <v>19.84602984134927</v>
+        <v>20.81796006855362</v>
       </c>
       <c r="D3" t="n">
-        <v>46.28449551671588</v>
+        <v>37.43894870145211</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.04947260030661</v>
+        <v>23.75142220884308</v>
       </c>
       <c r="C4" t="n">
-        <v>47.43903081691013</v>
+        <v>52.86318688287376</v>
       </c>
       <c r="D4" t="n">
-        <v>34.53592073999429</v>
+        <v>26.53369520267854</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.08745766113598</v>
+        <v>10.28380720198534</v>
       </c>
       <c r="C5" t="n">
-        <v>39.85895679242051</v>
+        <v>35.95650966803944</v>
       </c>
       <c r="D5" t="n">
-        <v>30.48326621686347</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.31700669748049</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72653281085917</v>
+        <v>16.73310464842647</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0318501462409</v>
+        <v>102.0719383554014</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181633202714792</v>
+        <v>4.183276162106616</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.602433237509047</v>
+        <v>4.990223580686537</v>
       </c>
       <c r="C2" t="n">
-        <v>8.926050127011999</v>
+        <v>5.128650006985338</v>
       </c>
       <c r="D2" t="n">
-        <v>28.57376693210342</v>
+        <v>17.71760081854219</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.25283324380595</v>
+        <v>19.36988220478957</v>
       </c>
       <c r="C3" t="n">
-        <v>23.92519155249477</v>
+        <v>18.53539665617978</v>
       </c>
       <c r="D3" t="n">
-        <v>64.90824946627787</v>
+        <v>45.14075944126834</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.46537377400877</v>
+        <v>30.69434197327653</v>
       </c>
       <c r="C4" t="n">
-        <v>48.19203130606743</v>
+        <v>52.44201711775187</v>
       </c>
       <c r="D4" t="n">
-        <v>49.13647259755286</v>
+        <v>38.63275390981624</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.2856728864026</v>
+        <v>22.82563412373834</v>
       </c>
       <c r="C5" t="n">
-        <v>65.65437772150545</v>
+        <v>68.9186888381261</v>
       </c>
       <c r="D5" t="n">
-        <v>35.46563581591603</v>
+        <v>31.95588777323368</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.740900721536855</v>
+        <v>10.02266231265569</v>
       </c>
       <c r="C6" t="n">
-        <v>38.64158963915446</v>
+        <v>35.86422538384024</v>
       </c>
       <c r="D6" t="n">
-        <v>38.35982804803563</v>
+        <v>37.8768081775462</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
         <v>34.28066633689012</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04394012493474</v>
+        <v>18.05681655549543</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7152284340981</v>
+        <v>117.7992318144225</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014646708311579</v>
+        <v>6.018938851831808</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.010259445398973</v>
+        <v>5.941537106101696</v>
       </c>
       <c r="C2" t="n">
-        <v>8.551022503989719</v>
+        <v>3.793473129209675</v>
       </c>
       <c r="D2" t="n">
-        <v>24.005694864243</v>
+        <v>36.24907048390498</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.3286077434822</v>
+        <v>16.09084487260522</v>
       </c>
       <c r="C3" t="n">
-        <v>28.11725424962865</v>
+        <v>18.15742379004476</v>
       </c>
       <c r="D3" t="n">
-        <v>67.91730617979435</v>
+        <v>45.69544689416779</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.35203081966388</v>
+        <v>24.96388062358789</v>
       </c>
       <c r="C4" t="n">
-        <v>45.26936839052468</v>
+        <v>41.03214529899544</v>
       </c>
       <c r="D4" t="n">
-        <v>60.63568345739575</v>
+        <v>45.21831750990383</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.315886081056</v>
+        <v>21.25483779694345</v>
       </c>
       <c r="C5" t="n">
-        <v>58.09492039880502</v>
+        <v>61.87464906015524</v>
       </c>
       <c r="D5" t="n">
-        <v>35.83379120500859</v>
+        <v>30.75324683553134</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.90819874188631</v>
+        <v>11.10945702125691</v>
       </c>
       <c r="C6" t="n">
-        <v>48.98626519880311</v>
+        <v>50.35482149852316</v>
       </c>
       <c r="D6" t="n">
-        <v>31.75855648468008</v>
+        <v>30.71201343195298</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>23.41566449399068</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.049039941165295</v>
+        <v>7.056987141290099</v>
       </c>
       <c r="C21" t="n">
-        <v>66.08474944842463</v>
+        <v>66.15925444959467</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405649963228309</v>
+        <v>4.410616963306312</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.303401098341269</v>
+        <v>5.448699758569798</v>
       </c>
       <c r="C2" t="n">
-        <v>4.748713645441821</v>
+        <v>5.817836895366598</v>
       </c>
       <c r="D2" t="n">
-        <v>19.95696733192916</v>
+        <v>27.84825537866502</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.35868206941536</v>
+        <v>19.03608798534566</v>
       </c>
       <c r="C3" t="n">
-        <v>31.46010518258904</v>
+        <v>16.00739631774425</v>
       </c>
       <c r="D3" t="n">
-        <v>71.6724911485384</v>
+        <v>65.10459900712723</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.58925391119311</v>
+        <v>29.3032054763588</v>
       </c>
       <c r="C4" t="n">
-        <v>60.45700537522283</v>
+        <v>43.90375733391736</v>
       </c>
       <c r="D4" t="n">
-        <v>82.16639235923255</v>
+        <v>58.23629206821654</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.5808190924824</v>
+        <v>30.87596529856219</v>
       </c>
       <c r="C5" t="n">
-        <v>73.82742735936016</v>
+        <v>69.94952392758525</v>
       </c>
       <c r="D5" t="n">
-        <v>49.89732706834415</v>
+        <v>41.13522880794136</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.68305972244431</v>
+        <v>21.09186767803848</v>
       </c>
       <c r="C6" t="n">
-        <v>74.58631833474294</v>
+        <v>79.17500710439252</v>
       </c>
       <c r="D6" t="n">
-        <v>36.46800022195202</v>
+        <v>34.05290086950487</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.881290643244144</v>
       </c>
       <c r="C7" t="n">
-        <v>51.50248456478767</v>
+        <v>52.64033015400972</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>26.95388322009618</v>
+        <v>26.28629478120835</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.267694172732917</v>
+        <v>7.279270731696224</v>
       </c>
       <c r="C21" t="n">
-        <v>75.40232704210402</v>
+        <v>75.52243384134833</v>
       </c>
       <c r="D21" t="n">
-        <v>5.450770629549688</v>
+        <v>5.459453048772168</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.818998569520092</v>
+        <v>6.48837057736717</v>
       </c>
       <c r="C2" t="n">
-        <v>4.221515128261284</v>
+        <v>8.120035261825368</v>
       </c>
       <c r="D2" t="n">
-        <v>23.15844659547801</v>
+        <v>20.13760890951058</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.31450342272425</v>
+        <v>18.94773069196344</v>
       </c>
       <c r="C3" t="n">
-        <v>23.699389580518</v>
+        <v>20.02765316663493</v>
       </c>
       <c r="D3" t="n">
-        <v>71.0098114481718</v>
+        <v>72.27626598665017</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.06446085777758</v>
+        <v>33.6425303291297</v>
       </c>
       <c r="C4" t="n">
-        <v>71.07558854435634</v>
+        <v>41.69580674706629</v>
       </c>
       <c r="D4" t="n">
-        <v>99.66408169202344</v>
+        <v>77.77601662584082</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.20761609614836</v>
+        <v>38.43542262126263</v>
       </c>
       <c r="C5" t="n">
-        <v>94.39504176333082</v>
+        <v>75.74183538264143</v>
       </c>
       <c r="D5" t="n">
-        <v>68.08420328951631</v>
+        <v>52.40078371417351</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.29691407950582</v>
+        <v>32.20132469929539</v>
       </c>
       <c r="C6" t="n">
-        <v>98.25429198872504</v>
+        <v>97.32850390362032</v>
       </c>
       <c r="D6" t="n">
-        <v>43.43153668817465</v>
+        <v>39.64788103600744</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>18.20552942755285</v>
       </c>
       <c r="C7" t="n">
-        <v>82.34408869370121</v>
+        <v>87.0751308804666</v>
       </c>
       <c r="D7" t="n">
-        <v>36.71049190490098</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>49.31809592283852</v>
+        <v>50.23603002630928</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>28.95468504135117</v>
+        <v>28.73281006019139</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
         <v>34.02246669067321</v>
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.473766300294549</v>
+        <v>7.490024793561986</v>
       </c>
       <c r="C21" t="n">
-        <v>85.01409166585049</v>
+        <v>84.26277892757234</v>
       </c>
       <c r="D21" t="n">
-        <v>6.53954551275773</v>
+        <v>6.553771694366738</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_61_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_61_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497615180899</v>
+        <v>10.84497639134156</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907131328867</v>
+        <v>37.78907214793443</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.270422587024377</v>
+        <v>0.8344855486097887</v>
       </c>
       <c r="C2" t="n">
-        <v>6.160466844148735</v>
+        <v>2.367975462643307</v>
       </c>
       <c r="D2" t="n">
-        <v>33.17227317879548</v>
+        <v>9.627999735548469</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.65597169735289</v>
+        <v>7.878525326580654</v>
       </c>
       <c r="C3" t="n">
-        <v>26.51209675318512</v>
+        <v>22.47220495020949</v>
       </c>
       <c r="D3" t="n">
-        <v>71.50559403881644</v>
+        <v>58.98340207114836</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.35273482992764</v>
+        <v>13.74544960715959</v>
       </c>
       <c r="C4" t="n">
-        <v>46.30314872309656</v>
+        <v>88.71366779885453</v>
       </c>
       <c r="D4" t="n">
-        <v>95.49067220127026</v>
+        <v>77.96745742816894</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.47317100238052</v>
+        <v>11.73188506574938</v>
       </c>
       <c r="C5" t="n">
-        <v>75.69274799742909</v>
+        <v>115.03628724512</v>
       </c>
       <c r="D5" t="n">
-        <v>67.07791189266334</v>
+        <v>50.020045531375</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.2642386678252</v>
+        <v>8.211337798320324</v>
       </c>
       <c r="C6" t="n">
-        <v>109.6857622569749</v>
+        <v>61.50453017565419</v>
       </c>
       <c r="D6" t="n">
-        <v>47.0944373727195</v>
+        <v>30.71201343195298</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.68568617038755</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>115.2817241711817</v>
+        <v>29.40432548989622</v>
       </c>
       <c r="D7" t="n">
-        <v>38.92629647338602</v>
+        <v>29.76364514965055</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.01935721664445</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>83.11476064153496</v>
+        <v>26.95388322009618</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>46.14999608123405</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.687964943231894</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.21657493668671</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.687964943231894</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.149086782325274</v>
+        <v>0.6351907646476863</v>
       </c>
       <c r="C2" t="n">
-        <v>6.595381077130072</v>
+        <v>6.589490590904591</v>
       </c>
       <c r="D2" t="n">
-        <v>30.74637460160161</v>
+        <v>15.8365722172053</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.73942025221387</v>
+        <v>5.12472301616835</v>
       </c>
       <c r="C3" t="n">
-        <v>25.03456645829367</v>
+        <v>14.43169125242811</v>
       </c>
       <c r="D3" t="n">
-        <v>79.53138152103412</v>
+        <v>52.99964981376405</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.98636300979434</v>
+        <v>14.81751810019711</v>
       </c>
       <c r="C4" t="n">
-        <v>56.41122308602172</v>
+        <v>70.56507973814799</v>
       </c>
       <c r="D4" t="n">
-        <v>106.4155606541288</v>
+        <v>90.06651613530664</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.79286090106649</v>
+        <v>16.41973035352791</v>
       </c>
       <c r="C5" t="n">
-        <v>79.66882619962867</v>
+        <v>143.6051454387022</v>
       </c>
       <c r="D5" t="n">
-        <v>84.03760348352698</v>
+        <v>66.70975650357077</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.47557646614552</v>
+        <v>12.15600007398401</v>
       </c>
       <c r="C6" t="n">
-        <v>115.2404907676034</v>
+        <v>125.5046630155038</v>
       </c>
       <c r="D6" t="n">
-        <v>55.62778841803278</v>
+        <v>39.1246095096439</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.74663664350886</v>
+        <v>7.785259294677205</v>
       </c>
       <c r="C7" t="n">
-        <v>136.7810171464826</v>
+        <v>60.96456893831842</v>
       </c>
       <c r="D7" t="n">
-        <v>43.35790561035613</v>
+        <v>32.39865598784899</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.03041848329842</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>115.6596970373167</v>
+        <v>33.62976760897448</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.31718662392973</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>73.21874378272709</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>41.99425804915732</v>
+        <v>35.44600086183109</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>38.61999118966103</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.870858954790839</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.337309042932</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.854716324139694</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.347800729210629</v>
+        <v>0.3288854809226814</v>
       </c>
       <c r="C2" t="n">
-        <v>7.403359437725197</v>
+        <v>2.622248118043231</v>
       </c>
       <c r="D2" t="n">
-        <v>32.59991426721958</v>
+        <v>10.68534201302228</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.92733497435251</v>
+        <v>4.363868545377072</v>
       </c>
       <c r="C3" t="n">
-        <v>25.11310627463341</v>
+        <v>21.33828635180442</v>
       </c>
       <c r="D3" t="n">
-        <v>83.80689277302896</v>
+        <v>54.90914909852411</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.76488893926206</v>
+        <v>16.10655283587317</v>
       </c>
       <c r="C4" t="n">
-        <v>58.51707191163113</v>
+        <v>62.90744764502287</v>
       </c>
       <c r="D4" t="n">
-        <v>118.5911956821977</v>
+        <v>97.14982582144738</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.27177385428968</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="C5" t="n">
-        <v>89.68265278294614</v>
+        <v>159.0185843953771</v>
       </c>
       <c r="D5" t="n">
-        <v>98.02750826904405</v>
+        <v>75.86455384567229</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.91584140600459</v>
+        <v>10.38492721552276</v>
       </c>
       <c r="C6" t="n">
-        <v>120.6744643106095</v>
+        <v>162.4154314520711</v>
       </c>
       <c r="D6" t="n">
-        <v>66.69699378341556</v>
+        <v>39.92964262712628</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.90928796724435</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>149.6566382876795</v>
+        <v>59.46740368934205</v>
       </c>
       <c r="D7" t="n">
-        <v>47.84940135728529</v>
+        <v>33.95570784678443</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.54217107911827</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>145.7011767872691</v>
+        <v>37.80219535202343</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.42031119060464</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>103.1718662392973</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>60.78490910844128</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>40.15937158992001</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.03911620179511</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.5329582494584</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.04889525224389</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.621307428067988</v>
+        <v>0.5379977419272521</v>
       </c>
       <c r="C2" t="n">
-        <v>4.974515617418588</v>
+        <v>5.819800390775092</v>
       </c>
       <c r="D2" t="n">
-        <v>26.72317250959818</v>
+        <v>10.90132650795658</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.38446955163303</v>
+        <v>2.635992585902686</v>
       </c>
       <c r="C3" t="n">
-        <v>37.70402058159875</v>
+        <v>14.88820393490288</v>
       </c>
       <c r="D3" t="n">
-        <v>90.80675390430872</v>
+        <v>51.24232142316227</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.63204989955247</v>
+        <v>12.4053639908627</v>
       </c>
       <c r="C4" t="n">
-        <v>77.9036438273929</v>
+        <v>58.13419030697488</v>
       </c>
       <c r="D4" t="n">
-        <v>113.2946668177862</v>
+        <v>102.510168286635</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.05406254365837</v>
+        <v>20.49398332615217</v>
       </c>
       <c r="C5" t="n">
-        <v>72.10936887692823</v>
+        <v>137.4937659797658</v>
       </c>
       <c r="D5" t="n">
-        <v>67.12699927787567</v>
+        <v>92.72607066611126</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.74597369097411</v>
+        <v>15.8994040702771</v>
       </c>
       <c r="C6" t="n">
-        <v>98.576305235718</v>
+        <v>212.005471488986</v>
       </c>
       <c r="D6" t="n">
-        <v>31.51704654943536</v>
+        <v>53.53470231257858</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.24167416616073</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="C7" t="n">
-        <v>102.4659896399438</v>
+        <v>144.5063898312007</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>76.02163347835176</v>
+        <v>57.49605429921444</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>46.37187106239383</v>
+        <v>36.94218436310322</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>36.78510473042374</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.560218086226434</v>
+        <v>0.3396847056693963</v>
       </c>
       <c r="C2" t="n">
-        <v>2.358157985600839</v>
+        <v>3.262347621212151</v>
       </c>
       <c r="D2" t="n">
-        <v>19.24912723716721</v>
+        <v>8.600109889202058</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.10605411425443</v>
+        <v>2.316924582022473</v>
       </c>
       <c r="C3" t="n">
-        <v>28.80447764260142</v>
+        <v>19.34042977366217</v>
       </c>
       <c r="D3" t="n">
-        <v>91.39580252685681</v>
+        <v>49.16592502868026</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.97810811753286</v>
+        <v>9.661379157492862</v>
       </c>
       <c r="C4" t="n">
-        <v>87.98619275000765</v>
+        <v>49.08542171693203</v>
       </c>
       <c r="D4" t="n">
-        <v>130.8816951916635</v>
+        <v>105.0882377579871</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.95650966803944</v>
+        <v>21.23029410433728</v>
       </c>
       <c r="C5" t="n">
-        <v>106.8877812998715</v>
+        <v>129.885221271853</v>
       </c>
       <c r="D5" t="n">
-        <v>85.16661334341082</v>
+        <v>105.7096840547753</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.66296710446964</v>
+        <v>19.80381469006666</v>
       </c>
       <c r="C6" t="n">
-        <v>111.5373384271844</v>
+        <v>225.6910344861865</v>
       </c>
       <c r="D6" t="n">
-        <v>39.56737772425921</v>
+        <v>64.32214608684252</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.92416874706152</v>
+        <v>8.863218273940204</v>
       </c>
       <c r="C7" t="n">
-        <v>122.5280039762274</v>
+        <v>207.9263097778404</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>41.9206269713388</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>99.05343461998193</v>
+        <v>95.46514676095984</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>40.97324043674063</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>52.91718300660731</v>
+        <v>48.14687091167205</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
         <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.17539834835746</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.645630136495907</v>
+        <v>1.353830084156352</v>
       </c>
       <c r="C2" t="n">
-        <v>5.731443097392879</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="D2" t="n">
-        <v>18.30174070256904</v>
+        <v>8.540223279243003</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.23520284285851</v>
+        <v>1.722967220953152</v>
       </c>
       <c r="C3" t="n">
-        <v>18.27032477603314</v>
+        <v>15.63924092865169</v>
       </c>
       <c r="D3" t="n">
-        <v>85.80474935117122</v>
+        <v>44.89532251520664</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.61021477034756</v>
+        <v>7.134360566761571</v>
       </c>
       <c r="C4" t="n">
-        <v>79.61384832819084</v>
+        <v>49.13647259755286</v>
       </c>
       <c r="D4" t="n">
-        <v>145.3418571275148</v>
+        <v>105.815712806834</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.49771469498668</v>
+        <v>18.67775007329557</v>
       </c>
       <c r="C5" t="n">
-        <v>134.5730665596316</v>
+        <v>110.127548723886</v>
       </c>
       <c r="D5" t="n">
-        <v>109.7348496421873</v>
+        <v>118.202423591316</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.22398701195107</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="C6" t="n">
-        <v>140.8807955594173</v>
+        <v>219.774041072691</v>
       </c>
       <c r="D6" t="n">
-        <v>54.37998708593508</v>
+        <v>80.18129850124551</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.56591295046944</v>
+        <v>14.85187926984575</v>
       </c>
       <c r="C7" t="n">
-        <v>142.7696781423882</v>
+        <v>264.2197231393526</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>49.34656660626167</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.18487166803466</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>129.4287085893783</v>
+        <v>178.1626646281899</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>42.89255719854314</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>83.42499291607693</v>
+        <v>79.43124325520091</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>43.37655881673681</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>46.12250714551515</v>
+        <v>44.27191272300992</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
+        <v>33.05151821117311</v>
+      </c>
+      <c r="D11" t="n">
         <v>34.11769621798515</v>
-      </c>
-      <c r="D11" t="n">
-        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.8226478228966</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>42.57152569925444</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.731222113214627</v>
+        <v>0.8874999246391165</v>
       </c>
       <c r="C2" t="n">
-        <v>2.642864819832413</v>
+        <v>3.406664533736432</v>
       </c>
       <c r="D2" t="n">
-        <v>12.63509295365645</v>
+        <v>6.14966761940202</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.95049600862693</v>
+        <v>3.166136346195964</v>
       </c>
       <c r="C3" t="n">
-        <v>21.25483779694344</v>
+        <v>22.16295442337174</v>
       </c>
       <c r="D3" t="n">
-        <v>84.38121518001336</v>
+        <v>47.6442160870977</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.26860762699868</v>
+        <v>12.35431311024186</v>
       </c>
       <c r="C4" t="n">
-        <v>74.80230282967722</v>
+        <v>68.3316037109865</v>
       </c>
       <c r="D4" t="n">
-        <v>155.3605924493535</v>
+        <v>111.6099877572986</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.38757902566179</v>
+        <v>15.04528356758237</v>
       </c>
       <c r="C5" t="n">
-        <v>157.3005259129452</v>
+        <v>175.143790437631</v>
       </c>
       <c r="D5" t="n">
-        <v>119.65050145508</v>
+        <v>111.5019955098315</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.26045054572845</v>
+        <v>9.217629195173304</v>
       </c>
       <c r="C6" t="n">
-        <v>176.5035110080129</v>
+        <v>232.1715510819197</v>
       </c>
       <c r="D6" t="n">
-        <v>52.89067581859268</v>
+        <v>68.46806664187682</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>158.4000833417016</v>
+        <v>125.282788034344</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>37.36924461445059</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>102.0575825949772</v>
+        <v>58.4974369575462</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>35.16718451382499</v>
+        <v>33.72499713628642</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
+        <v>25.90832191507333</v>
+      </c>
+      <c r="D10" t="n">
         <v>26.76244241776806</v>
-      </c>
-      <c r="D10" t="n">
-        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.56913593102267</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>35.83379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.650137964389641</v>
+        <v>0.4388412237983242</v>
       </c>
       <c r="C2" t="n">
-        <v>4.063453747877548</v>
+        <v>1.884955592153876</v>
       </c>
       <c r="D2" t="n">
-        <v>14.49550485320415</v>
+        <v>5.28474789196058</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.29562923216531</v>
+        <v>3.112140222462389</v>
       </c>
       <c r="C3" t="n">
-        <v>15.38889526406875</v>
+        <v>17.16094987023424</v>
       </c>
       <c r="D3" t="n">
-        <v>75.82528393750241</v>
+        <v>41.59174149041613</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.46531702074653</v>
+        <v>8.691412425697012</v>
       </c>
       <c r="C4" t="n">
-        <v>64.38792318302706</v>
+        <v>59.52532680389261</v>
       </c>
       <c r="D4" t="n">
-        <v>161.0782910788869</v>
+        <v>106.0071536091621</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.97220193577417</v>
+        <v>13.6217493964245</v>
       </c>
       <c r="C5" t="n">
-        <v>149.3238258159399</v>
+        <v>135.2357462599982</v>
       </c>
       <c r="D5" t="n">
-        <v>143.5069706682775</v>
+        <v>114.6435881634213</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.65166915810419</v>
+        <v>9.096874227550947</v>
       </c>
       <c r="C6" t="n">
-        <v>211.7639615537413</v>
+        <v>214.0985575944402</v>
       </c>
       <c r="D6" t="n">
-        <v>73.33851700264525</v>
+        <v>72.29197394991814</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.82246789644735</v>
+        <v>3.653083207502381</v>
       </c>
       <c r="C7" t="n">
-        <v>204.2732265703381</v>
+        <v>162.2927129890402</v>
       </c>
       <c r="D7" t="n">
-        <v>40.24380189248525</v>
+        <v>36.89015173477814</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>148.2046334330985</v>
+        <v>69.34574908947344</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>27.70492021384499</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>69.66874408417063</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>21.41093568191868</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>19.50241814486289</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52209415667683</v>
+        <v>14.03801042302514</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.66544501703009</v>
+        <v>0.5929756133650734</v>
       </c>
       <c r="C2" t="n">
-        <v>2.641883072128167</v>
+        <v>4.571999058677396</v>
       </c>
       <c r="D2" t="n">
-        <v>10.44972256400305</v>
+        <v>12.86580366415445</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.24515918862122</v>
+        <v>2.22856728864026</v>
       </c>
       <c r="C3" t="n">
-        <v>15.74723317611884</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D3" t="n">
-        <v>71.29451828240336</v>
+        <v>36.37866118086556</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.28365263773187</v>
+        <v>7.300275928779282</v>
       </c>
       <c r="C4" t="n">
-        <v>54.59891682398212</v>
+        <v>49.69803228438204</v>
       </c>
       <c r="D4" t="n">
-        <v>162.5715293370463</v>
+        <v>103.186592454861</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.54362015737481</v>
+        <v>13.71992416684918</v>
       </c>
       <c r="C5" t="n">
-        <v>142.4025045009999</v>
+        <v>122.1539581009094</v>
       </c>
       <c r="D5" t="n">
-        <v>161.0311671890831</v>
+        <v>127.430852011236</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.38627848278806</v>
+        <v>14.00757624419349</v>
       </c>
       <c r="C6" t="n">
-        <v>231.1250080291927</v>
+        <v>215.708623829405</v>
       </c>
       <c r="D6" t="n">
-        <v>87.86936477320229</v>
+        <v>91.29075552250242</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.28348840681585</v>
+        <v>7.186393195086651</v>
       </c>
       <c r="C7" t="n">
-        <v>246.4333999815131</v>
+        <v>244.9362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>45.51382356888213</v>
+        <v>48.26860762699867</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>2.503456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>185.4226889010951</v>
+        <v>146.7860080004618</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>82.98124295375739</v>
+        <v>59.57343244140068</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>23.40781051235669</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>28.75539025738908</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>13.88583952886689</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.712969817461437</v>
+        <v>0.7549639845657972</v>
       </c>
       <c r="C2" t="n">
-        <v>9.352128630655116</v>
+        <v>18.04648629946487</v>
       </c>
       <c r="D2" t="n">
-        <v>20.49300157844792</v>
+        <v>11.72010409329842</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.69752389610075</v>
+        <v>2.115666302651876</v>
       </c>
       <c r="C3" t="n">
-        <v>13.02288329683394</v>
+        <v>14.96183501272139</v>
       </c>
       <c r="D3" t="n">
-        <v>64.86407081958676</v>
+        <v>38.06235849364884</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.42556408649115</v>
+        <v>5.743224069843841</v>
       </c>
       <c r="C4" t="n">
-        <v>47.42626809675492</v>
+        <v>37.57344813693393</v>
       </c>
       <c r="D4" t="n">
-        <v>159.3425611377786</v>
+        <v>98.47714871758905</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.43915399009715</v>
+        <v>12.4681958439345</v>
       </c>
       <c r="C5" t="n">
-        <v>123.6265796572796</v>
+        <v>105.8324025178062</v>
       </c>
       <c r="D5" t="n">
-        <v>177.9663150873406</v>
+        <v>135.8247948825462</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.61649047166733</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="C6" t="n">
-        <v>230.0382133205914</v>
+        <v>205.6859615167493</v>
       </c>
       <c r="D6" t="n">
-        <v>110.4102920627091</v>
+        <v>108.357457613129</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.99185258539232</v>
+        <v>11.91743538185203</v>
       </c>
       <c r="C7" t="n">
-        <v>286.9167483138345</v>
+        <v>282.0659329071511</v>
       </c>
       <c r="D7" t="n">
-        <v>55.87420709179872</v>
+        <v>62.34196096737671</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>242.5849489808656</v>
+        <v>238.1621755732337</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>139.7812381306608</v>
+        <v>120.5890522603399</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>25.5156228333746</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>56.65666001208344</v>
+        <v>49.25428232206248</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>25.41057582902019</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.558254590817941</v>
+        <v>1.981166867170063</v>
       </c>
       <c r="C2" t="n">
-        <v>8.06113039957056</v>
+        <v>2.269800692218626</v>
       </c>
       <c r="D2" t="n">
-        <v>4.53076565509903</v>
+        <v>12.1746532803647</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.629120351972958</v>
+        <v>0.4800746273766903</v>
       </c>
       <c r="C2" t="n">
-        <v>5.236642254452487</v>
+        <v>21.97445886415635</v>
       </c>
       <c r="D2" t="n">
-        <v>15.08357172804799</v>
+        <v>16.61018940815179</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.68832831386403</v>
+        <v>2.312015843501239</v>
       </c>
       <c r="C3" t="n">
-        <v>22.22185928562655</v>
+        <v>43.84976121018379</v>
       </c>
       <c r="D3" t="n">
-        <v>72.35480580298993</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.01786105178824</v>
+        <v>4.849833658979244</v>
       </c>
       <c r="C4" t="n">
-        <v>68.54856995362505</v>
+        <v>37.43305821522663</v>
       </c>
       <c r="D4" t="n">
-        <v>165.1113106479328</v>
+        <v>94.61004451056087</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.83441309981433</v>
+        <v>10.87285582453343</v>
       </c>
       <c r="C5" t="n">
-        <v>190.4835983164874</v>
+        <v>87.8173321448772</v>
       </c>
       <c r="D5" t="n">
-        <v>162.8228567493335</v>
+        <v>140.4144653999001</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.33966901013618</v>
+        <v>16.82519215538184</v>
       </c>
       <c r="C6" t="n">
-        <v>236.317471636954</v>
+        <v>187.1299481587803</v>
       </c>
       <c r="D6" t="n">
-        <v>85.73602701187396</v>
+        <v>124.4581199627767</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.467753875577986</v>
+        <v>15.63040519931347</v>
       </c>
       <c r="C7" t="n">
-        <v>170.5570651633899</v>
+        <v>292.7257494798629</v>
       </c>
       <c r="D7" t="n">
-        <v>34.6743471662931</v>
+        <v>75.57690176832796</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>102.9755166984479</v>
+        <v>304.8375709071558</v>
       </c>
       <c r="D8" t="n">
-        <v>24.86766934857171</v>
+        <v>43.47669708257</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>43.26562132615692</v>
+        <v>201.1296704213397</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>23.06125357275758</v>
+        <v>89.96735961717772</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>39.09319358310798</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>20.25738212942868</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>16.05550195525234</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.609305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.424556976591127</v>
+        <v>3.602032326881548</v>
       </c>
       <c r="C2" t="n">
-        <v>7.872634840355172</v>
+        <v>10.7864620265597</v>
       </c>
       <c r="D2" t="n">
-        <v>22.31807056064274</v>
+        <v>22.0068565383965</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.689849840916018</v>
+        <v>3.288854809226815</v>
       </c>
       <c r="C3" t="n">
-        <v>20.63633674326795</v>
+        <v>4.481678269886689</v>
       </c>
       <c r="D3" t="n">
-        <v>6.940956269024949</v>
+        <v>11.31955102996572</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39905899333275</v>
+        <v>11.67880320311019</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14801472980088</v>
+        <v>59.95118977596563</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576359881568559</v>
+        <v>0.7785868802073458</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.998478472948011</v>
+        <v>2.132356013624072</v>
       </c>
       <c r="C2" t="n">
-        <v>4.330489123432681</v>
+        <v>8.101382055444679</v>
       </c>
       <c r="D2" t="n">
-        <v>23.75044046113884</v>
+        <v>19.37380919560655</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.15113239319178</v>
+        <v>9.066440048719294</v>
       </c>
       <c r="C3" t="n">
-        <v>26.93424826601124</v>
+        <v>29.55060589782899</v>
       </c>
       <c r="D3" t="n">
-        <v>24.00864010735575</v>
+        <v>27.83745615391831</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.38434637844601</v>
+        <v>4.301036692305276</v>
       </c>
       <c r="C4" t="n">
-        <v>31.98337670895259</v>
+        <v>7.874598335763666</v>
       </c>
       <c r="D4" t="n">
-        <v>18.71014774753571</v>
+        <v>20.20338600569511</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>21.07812321017901</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4413483342185</v>
+        <v>13.63156929761332</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14646965406112</v>
+        <v>73.77084561061324</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250810175624948</v>
+        <v>1.603714035013331</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.602834148136546</v>
+        <v>1.964477156197868</v>
       </c>
       <c r="C2" t="n">
-        <v>4.351105825221864</v>
+        <v>5.98964274360979</v>
       </c>
       <c r="D2" t="n">
-        <v>21.09481292115122</v>
+        <v>19.27465267747763</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.20789383358884</v>
+        <v>8.138688468206059</v>
       </c>
       <c r="C3" t="n">
-        <v>20.81796006855362</v>
+        <v>30.91032646821083</v>
       </c>
       <c r="D3" t="n">
-        <v>37.43894870145211</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.75142220884308</v>
+        <v>12.22668590868978</v>
       </c>
       <c r="C4" t="n">
-        <v>52.86318688287376</v>
+        <v>49.40448972081224</v>
       </c>
       <c r="D4" t="n">
-        <v>26.53369520267854</v>
+        <v>29.9030533236536</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.28380720198534</v>
+        <v>4.712388980384691</v>
       </c>
       <c r="C5" t="n">
-        <v>35.95650966803944</v>
+        <v>10.84831213192726</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>27.41530464109218</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.18437294641592</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73310464842647</v>
+        <v>14.845848088101</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0719383554014</v>
+        <v>87.42554985215031</v>
       </c>
       <c r="D21" t="n">
-        <v>4.183276162106616</v>
+        <v>2.474308014683499</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.990223580686537</v>
+        <v>1.66504410640259</v>
       </c>
       <c r="C2" t="n">
-        <v>5.128650006985338</v>
+        <v>3.663882432249096</v>
       </c>
       <c r="D2" t="n">
-        <v>17.71760081854219</v>
+        <v>23.03769162785565</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.36988220478957</v>
+        <v>7.392560212978482</v>
       </c>
       <c r="C3" t="n">
-        <v>18.53539665617978</v>
+        <v>26.24211613451724</v>
       </c>
       <c r="D3" t="n">
-        <v>45.14075944126834</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.69434197327653</v>
+        <v>14.42187377538565</v>
       </c>
       <c r="C4" t="n">
-        <v>52.44201711775187</v>
+        <v>66.20022944506667</v>
       </c>
       <c r="D4" t="n">
-        <v>38.63275390981624</v>
+        <v>41.61923042613503</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.82563412373834</v>
+        <v>11.90369091399258</v>
       </c>
       <c r="C5" t="n">
-        <v>68.9186888381261</v>
+        <v>57.48132808365076</v>
       </c>
       <c r="D5" t="n">
-        <v>31.95588777323368</v>
+        <v>32.34858685493241</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.02266231265569</v>
+        <v>5.594980166502573</v>
       </c>
       <c r="C6" t="n">
-        <v>35.86422538384024</v>
+        <v>14.24908617943821</v>
       </c>
       <c r="D6" t="n">
-        <v>37.8768081775462</v>
+        <v>34.01264921363075</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05681655549543</v>
+        <v>16.09445936662251</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7992318144225</v>
+        <v>101.6492170523527</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018938851831808</v>
+        <v>3.388307235078423</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.941537106101696</v>
+        <v>2.183406894244906</v>
       </c>
       <c r="C2" t="n">
-        <v>3.793473129209675</v>
+        <v>5.779548734900973</v>
       </c>
       <c r="D2" t="n">
-        <v>36.24907048390498</v>
+        <v>20.40857127588269</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.09084487260522</v>
+        <v>6.46971737098648</v>
       </c>
       <c r="C3" t="n">
-        <v>18.15742379004476</v>
+        <v>19.18335014098268</v>
       </c>
       <c r="D3" t="n">
-        <v>45.69544689416779</v>
+        <v>51.82155256866788</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.96388062358789</v>
+        <v>14.48568737616169</v>
       </c>
       <c r="C4" t="n">
-        <v>41.03214529899544</v>
+        <v>65.9322123218073</v>
       </c>
       <c r="D4" t="n">
-        <v>45.21831750990383</v>
+        <v>53.28435664799564</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.25483779694345</v>
+        <v>17.00877897607599</v>
       </c>
       <c r="C5" t="n">
-        <v>61.87464906015524</v>
+        <v>93.14331344041615</v>
       </c>
       <c r="D5" t="n">
-        <v>30.75324683553134</v>
+        <v>40.05530633326987</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.10945702125691</v>
+        <v>10.86794708601219</v>
       </c>
       <c r="C6" t="n">
-        <v>50.35482149852316</v>
+        <v>54.66174867705392</v>
       </c>
       <c r="D6" t="n">
-        <v>30.71201343195298</v>
+        <v>36.8302651248191</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>23.41566449399068</v>
+        <v>19.3433750167749</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.056987141290099</v>
+        <v>17.3711391899558</v>
       </c>
       <c r="C21" t="n">
-        <v>66.15925444959467</v>
+        <v>115.5180756132061</v>
       </c>
       <c r="D21" t="n">
-        <v>4.410616963306312</v>
+        <v>4.34278479748895</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.448699758569798</v>
+        <v>1.866302385773186</v>
       </c>
       <c r="C2" t="n">
-        <v>5.817836895366598</v>
+        <v>5.933683124467722</v>
       </c>
       <c r="D2" t="n">
-        <v>27.84825537866502</v>
+        <v>17.38675184221101</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.03608798534566</v>
+        <v>6.960591223109886</v>
       </c>
       <c r="C3" t="n">
-        <v>16.00739631774425</v>
+        <v>20.95049600862693</v>
       </c>
       <c r="D3" t="n">
-        <v>65.10459900712723</v>
+        <v>55.48347150550849</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.3032054763588</v>
+        <v>13.47743248390021</v>
       </c>
       <c r="C4" t="n">
-        <v>43.90375733391736</v>
+        <v>56.23254500384881</v>
       </c>
       <c r="D4" t="n">
-        <v>58.23629206821654</v>
+        <v>65.21749999311561</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.87596529856219</v>
+        <v>19.315886081056</v>
       </c>
       <c r="C5" t="n">
-        <v>69.94952392758525</v>
+        <v>107.108674533327</v>
       </c>
       <c r="D5" t="n">
-        <v>41.13522880794136</v>
+        <v>49.60280275707011</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.09186767803848</v>
+        <v>16.82519215538184</v>
       </c>
       <c r="C6" t="n">
-        <v>79.17500710439252</v>
+        <v>102.0781992967664</v>
       </c>
       <c r="D6" t="n">
-        <v>34.05290086950487</v>
+        <v>40.65417243286043</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.881290643244144</v>
+        <v>9.761517423326035</v>
       </c>
       <c r="C7" t="n">
-        <v>52.64033015400972</v>
+        <v>49.0471335564664</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>39.34550274309942</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>26.28629478120835</v>
+        <v>25.95250056176443</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>46.7341359652609</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.279270731696224</v>
+        <v>18.6708969529038</v>
       </c>
       <c r="C21" t="n">
-        <v>75.52243384134833</v>
+        <v>128.9180980081453</v>
       </c>
       <c r="D21" t="n">
-        <v>5.459453048772168</v>
+        <v>5.334541986543942</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.48837057736717</v>
+        <v>1.706277509980957</v>
       </c>
       <c r="C2" t="n">
-        <v>8.120035261825368</v>
+        <v>3.606941065402781</v>
       </c>
       <c r="D2" t="n">
-        <v>20.13760890951058</v>
+        <v>13.59818745152257</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.94773069196344</v>
+        <v>9.277515805132358</v>
       </c>
       <c r="C3" t="n">
-        <v>20.02765316663493</v>
+        <v>32.65783738177014</v>
       </c>
       <c r="D3" t="n">
-        <v>72.27626598665017</v>
+        <v>61.80101798233672</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.6425303291297</v>
+        <v>9.278497552836605</v>
       </c>
       <c r="C4" t="n">
-        <v>41.69580674706629</v>
+        <v>89.63258365002955</v>
       </c>
       <c r="D4" t="n">
-        <v>77.77601662584082</v>
+        <v>61.52907386826035</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.43542262126263</v>
+        <v>9.473865345981721</v>
       </c>
       <c r="C5" t="n">
-        <v>75.74183538264143</v>
+        <v>60.99107612633311</v>
       </c>
       <c r="D5" t="n">
-        <v>52.40078371417351</v>
+        <v>39.04901493641689</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.20132469929539</v>
+        <v>6.037748381117884</v>
       </c>
       <c r="C6" t="n">
-        <v>97.32850390362032</v>
+        <v>32.28182801104362</v>
       </c>
       <c r="D6" t="n">
-        <v>39.64788103600744</v>
+        <v>25.88181472705867</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>5.150248456478767</v>
+      </c>
+      <c r="C7" t="n">
         <v>18.20552942755285</v>
       </c>
-      <c r="C7" t="n">
-        <v>87.0751308804666</v>
-      </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>50.23603002630928</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>28.73281006019139</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.490024793561986</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.26277892757234</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.553771694366738</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
